--- a/frontend/public/DealFlow360_Seeded_Database.xlsx
+++ b/frontend/public/DealFlow360_Seeded_Database.xlsx
@@ -445,7 +445,7 @@
         <v>Export Timestamp</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-09-05T17:49:07.550Z</v>
+        <v>2026-09-05T17:50:18.460Z</v>
       </c>
     </row>
     <row r="4">
